--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16185" windowHeight="4995"/>
@@ -17,22 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>产品登记编码生成日</t>
-  </si>
-  <si>
-    <t>产品状态</t>
-  </si>
-  <si>
-    <t>目标客户类型</t>
-  </si>
-  <si>
-    <t>理财产品代码</t>
-  </si>
-  <si>
-    <t>行内标识码</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>产品登记编码</t>
   </si>
@@ -40,11 +25,12 @@
     <t>产品名称</t>
   </si>
   <si>
-    <t>发行机构名称</t>
+    <t>产品运作模式</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>产品运作模式</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>产品代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -184,7 +170,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -226,7 +212,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -261,7 +247,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -470,64 +456,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.75" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" style="6" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="19.25" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"01 封闭式净值型,02 封闭式非净值型,03 开放式净值型,04 开放式非净值型"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProRegistCode.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>产品登记编码</t>
   </si>
@@ -25,19 +25,34 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>发行机构名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行内标识码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理财产品代码</t>
+  </si>
+  <si>
     <t>产品运作模式</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标客户类型</t>
+  </si>
+  <si>
+    <t>产品状态</t>
+  </si>
+  <si>
+    <t>产品登记编码生成日</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +79,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -77,11 +93,6 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -456,19 +467,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.75" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.25" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="18.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15" style="5" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -477,10 +493,25 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
